--- a/极印版 aiken/AiKen JY Finance_261026.xlsx
+++ b/极印版 aiken/AiKen JY Finance_261026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a22fe4ae455d837/01 汉图/03 产品/06 Aiken/05. JY SI^MDO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\code_aiken\极印版 aiken\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{8DB45FD7-6C93-40B1-8089-220C39B19EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F1212B5-4ED0-4F98-9CFB-C1F6E5F51202}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A33A59-2569-431E-A683-4C15AC328D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16870" yWindow="80" windowWidth="17150" windowHeight="13550" tabRatio="787" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3274,7 +3274,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3768,80 +3768,83 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="22" fillId="13" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="22" fillId="13" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -4389,7 +4392,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="127"/>
-      <c r="G12" s="176" t="s">
+      <c r="G12" s="184" t="s">
         <v>163</v>
       </c>
       <c r="H12" s="129">
@@ -4398,7 +4401,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A13" s="180"/>
+      <c r="A13" s="188"/>
       <c r="B13" s="123" t="s">
         <v>33</v>
       </c>
@@ -4413,13 +4416,13 @@
         <v>7</v>
       </c>
       <c r="F13" s="127"/>
-      <c r="G13" s="177"/>
+      <c r="G13" s="185"/>
       <c r="H13" s="129">
         <v>300000</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A14" s="181"/>
+      <c r="A14" s="189"/>
       <c r="B14" s="123" t="s">
         <v>33</v>
       </c>
@@ -4434,7 +4437,7 @@
         <v>7</v>
       </c>
       <c r="F14" s="127"/>
-      <c r="G14" s="177"/>
+      <c r="G14" s="185"/>
       <c r="H14" s="129">
         <f>H12+H13</f>
         <v>1950000</v>
@@ -4442,7 +4445,7 @@
       <c r="I14" s="160"/>
     </row>
     <row r="15" spans="1:9" ht="16.5" customHeight="1">
-      <c r="A15" s="181"/>
+      <c r="A15" s="189"/>
       <c r="B15" s="123" t="s">
         <v>36</v>
       </c>
@@ -4611,11 +4614,11 @@
       <c r="C26" s="138" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="178" t="e">
+      <c r="D26" s="186" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E26" s="179"/>
+      <c r="E26" s="187"/>
       <c r="F26" s="139"/>
       <c r="G26" s="116"/>
       <c r="H26" s="116"/>
@@ -4867,7 +4870,7 @@
       <c r="F44" s="127"/>
     </row>
     <row r="45" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A45" s="180"/>
+      <c r="A45" s="188"/>
       <c r="B45" s="123" t="s">
         <v>33</v>
       </c>
@@ -4884,7 +4887,7 @@
       <c r="F45" s="127"/>
     </row>
     <row r="46" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A46" s="181"/>
+      <c r="A46" s="189"/>
       <c r="B46" s="123" t="s">
         <v>33</v>
       </c>
@@ -4901,7 +4904,7 @@
       <c r="F46" s="127"/>
     </row>
     <row r="47" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A47" s="181"/>
+      <c r="A47" s="189"/>
       <c r="B47" s="123" t="s">
         <v>36</v>
       </c>
@@ -5070,11 +5073,11 @@
       <c r="C58" s="138" t="s">
         <v>53</v>
       </c>
-      <c r="D58" s="178" t="e">
+      <c r="D58" s="186" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E58" s="179"/>
+      <c r="E58" s="187"/>
       <c r="F58" s="139"/>
       <c r="G58" s="116"/>
       <c r="H58" s="116"/>
@@ -5306,7 +5309,7 @@
       <c r="F78" s="127"/>
     </row>
     <row r="79" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A79" s="180"/>
+      <c r="A79" s="188"/>
       <c r="B79" s="123" t="s">
         <v>33</v>
       </c>
@@ -5323,7 +5326,7 @@
       <c r="F79" s="127"/>
     </row>
     <row r="80" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A80" s="181"/>
+      <c r="A80" s="189"/>
       <c r="B80" s="123" t="s">
         <v>33</v>
       </c>
@@ -5340,7 +5343,7 @@
       <c r="F80" s="127"/>
     </row>
     <row r="81" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A81" s="181"/>
+      <c r="A81" s="189"/>
       <c r="B81" s="123" t="s">
         <v>36</v>
       </c>
@@ -5509,11 +5512,11 @@
       <c r="C92" s="138" t="s">
         <v>53</v>
       </c>
-      <c r="D92" s="178" t="e">
+      <c r="D92" s="186" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="E92" s="179"/>
+      <c r="E92" s="187"/>
       <c r="F92" s="139"/>
       <c r="G92" s="116"/>
       <c r="H92" s="116"/>
@@ -6248,11 +6251,11 @@
     <row r="1" spans="2:8" ht="15" thickBot="1"/>
     <row r="2" spans="2:8">
       <c r="B2" s="97"/>
-      <c r="C2" s="185" t="s">
+      <c r="C2" s="193" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="186"/>
-      <c r="E2" s="187"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="195"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="98"/>
@@ -6279,10 +6282,10 @@
       <c r="D4" s="102">
         <v>2400</v>
       </c>
-      <c r="E4" s="183" t="s">
+      <c r="E4" s="191" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="182" t="s">
+      <c r="F4" s="190" t="s">
         <v>164</v>
       </c>
       <c r="G4" s="103"/>
@@ -6299,8 +6302,8 @@
       <c r="D5" s="102">
         <v>2400</v>
       </c>
-      <c r="E5" s="184"/>
-      <c r="F5" s="182"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="190"/>
       <c r="G5" s="103"/>
       <c r="H5" s="103"/>
     </row>
@@ -6315,8 +6318,8 @@
       <c r="D6" s="102">
         <v>2400</v>
       </c>
-      <c r="E6" s="184"/>
-      <c r="F6" s="182"/>
+      <c r="E6" s="192"/>
+      <c r="F6" s="190"/>
       <c r="G6" s="103"/>
       <c r="H6" s="103"/>
     </row>
@@ -6334,11 +6337,11 @@
     <row r="9" spans="2:8" ht="15" thickBot="1"/>
     <row r="10" spans="2:8">
       <c r="B10" s="97"/>
-      <c r="C10" s="185" t="s">
+      <c r="C10" s="193" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="186"/>
-      <c r="E10" s="187"/>
+      <c r="D10" s="194"/>
+      <c r="E10" s="195"/>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="107"/>
@@ -6365,10 +6368,10 @@
       <c r="D12" s="102">
         <v>3700</v>
       </c>
-      <c r="E12" s="183" t="s">
+      <c r="E12" s="191" t="s">
         <v>169</v>
       </c>
-      <c r="F12" s="182" t="s">
+      <c r="F12" s="190" t="s">
         <v>166</v>
       </c>
       <c r="G12" s="110"/>
@@ -6385,8 +6388,8 @@
       <c r="D13" s="102">
         <v>3700</v>
       </c>
-      <c r="E13" s="184"/>
-      <c r="F13" s="182"/>
+      <c r="E13" s="192"/>
+      <c r="F13" s="190"/>
       <c r="G13" s="110"/>
       <c r="H13" s="103"/>
     </row>
@@ -6401,8 +6404,8 @@
       <c r="D14" s="102">
         <v>3700</v>
       </c>
-      <c r="E14" s="184"/>
-      <c r="F14" s="182"/>
+      <c r="E14" s="192"/>
+      <c r="F14" s="190"/>
       <c r="G14" s="110"/>
       <c r="H14" s="103"/>
     </row>
@@ -6420,11 +6423,11 @@
     <row r="17" spans="2:8" ht="15" thickBot="1"/>
     <row r="18" spans="2:8">
       <c r="B18" s="97"/>
-      <c r="C18" s="185" t="s">
+      <c r="C18" s="193" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="186"/>
-      <c r="E18" s="187"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="195"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="98"/>
@@ -6451,10 +6454,10 @@
       <c r="D20" s="102">
         <v>1500</v>
       </c>
-      <c r="E20" s="183" t="s">
+      <c r="E20" s="191" t="s">
         <v>170</v>
       </c>
-      <c r="F20" s="182" t="s">
+      <c r="F20" s="190" t="s">
         <v>165</v>
       </c>
       <c r="G20" s="110"/>
@@ -6471,8 +6474,8 @@
       <c r="D21" s="102">
         <v>1500</v>
       </c>
-      <c r="E21" s="184"/>
-      <c r="F21" s="182"/>
+      <c r="E21" s="192"/>
+      <c r="F21" s="190"/>
       <c r="G21" s="110"/>
       <c r="H21" s="103"/>
     </row>
@@ -6487,8 +6490,8 @@
       <c r="D22" s="102">
         <v>1500</v>
       </c>
-      <c r="E22" s="184"/>
-      <c r="F22" s="182"/>
+      <c r="E22" s="192"/>
+      <c r="F22" s="190"/>
       <c r="G22" s="110"/>
       <c r="H22" s="103"/>
     </row>
@@ -6540,18 +6543,18 @@
       <c r="D1" s="82"/>
     </row>
     <row r="2" spans="2:8">
-      <c r="C2" s="175" t="s">
+      <c r="C2" s="196" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175" t="s">
+      <c r="D2" s="196"/>
+      <c r="E2" s="196" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175" t="s">
+      <c r="F2" s="196"/>
+      <c r="G2" s="196" t="s">
         <v>136</v>
       </c>
-      <c r="H2" s="175"/>
+      <c r="H2" s="196"/>
     </row>
     <row r="3" spans="2:8" ht="15" thickBot="1">
       <c r="C3" s="80" t="s">
@@ -6960,40 +6963,40 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="50.4" customHeight="1">
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="197" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="188"/>
-      <c r="D9" s="188"/>
-      <c r="E9" s="188"/>
-      <c r="F9" s="188"/>
+      <c r="C9" s="197"/>
+      <c r="D9" s="197"/>
+      <c r="E9" s="197"/>
+      <c r="F9" s="197"/>
     </row>
     <row r="10" spans="2:6" ht="33.65" customHeight="1">
-      <c r="B10" s="189" t="s">
+      <c r="B10" s="198" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="188"/>
-      <c r="D10" s="188"/>
-      <c r="E10" s="188"/>
-      <c r="F10" s="188"/>
+      <c r="C10" s="197"/>
+      <c r="D10" s="197"/>
+      <c r="E10" s="197"/>
+      <c r="F10" s="197"/>
     </row>
     <row r="11" spans="2:6" ht="33.65" customHeight="1">
-      <c r="B11" s="189" t="s">
+      <c r="B11" s="198" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="188"/>
-      <c r="D11" s="188"/>
-      <c r="E11" s="188"/>
-      <c r="F11" s="188"/>
+      <c r="C11" s="197"/>
+      <c r="D11" s="197"/>
+      <c r="E11" s="197"/>
+      <c r="F11" s="197"/>
     </row>
     <row r="12" spans="2:6" ht="50.4" customHeight="1">
-      <c r="B12" s="189" t="s">
+      <c r="B12" s="198" t="s">
         <v>161</v>
       </c>
-      <c r="C12" s="188"/>
-      <c r="D12" s="188"/>
-      <c r="E12" s="188"/>
-      <c r="F12" s="188"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="197"/>
+      <c r="E12" s="197"/>
+      <c r="F12" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7031,10 +7034,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:26" s="1" customFormat="1" ht="20">
-      <c r="B1" s="190" t="s">
+      <c r="B1" s="175" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="190"/>
+      <c r="C1" s="175"/>
     </row>
     <row r="2" spans="2:26" s="1" customFormat="1"/>
     <row r="3" spans="2:26" s="1" customFormat="1" ht="16.5">
@@ -7046,22 +7049,22 @@
         <v>600000</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="191" t="s">
+      <c r="F3" s="176" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="193" t="s">
+      <c r="G3" s="177"/>
+      <c r="H3" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="194"/>
-      <c r="J3" s="195" t="s">
+      <c r="I3" s="179"/>
+      <c r="J3" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="196"/>
-      <c r="M3" s="197" t="s">
+      <c r="K3" s="181"/>
+      <c r="M3" s="182" t="s">
         <v>138</v>
       </c>
-      <c r="N3" s="198"/>
+      <c r="N3" s="183"/>
     </row>
     <row r="4" spans="2:26" s="1" customFormat="1">
       <c r="B4" s="7" t="s">
@@ -8015,6 +8018,12 @@
         <f t="shared" si="8"/>
         <v>1212235.00596778</v>
       </c>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="F31" s="200"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="F32" s="200"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="77"/>
@@ -8168,10 +8177,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:26" s="1" customFormat="1" ht="20">
-      <c r="B1" s="190" t="s">
+      <c r="B1" s="175" t="s">
         <v>132</v>
       </c>
-      <c r="C1" s="190"/>
+      <c r="C1" s="175"/>
     </row>
     <row r="2" spans="2:26" s="1" customFormat="1"/>
     <row r="3" spans="2:26" s="1" customFormat="1" ht="16.5">
@@ -8183,22 +8192,22 @@
         <v>600000</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="191" t="s">
+      <c r="F3" s="176" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="193" t="s">
+      <c r="G3" s="177"/>
+      <c r="H3" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="194"/>
-      <c r="J3" s="195" t="s">
+      <c r="I3" s="179"/>
+      <c r="J3" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="196"/>
-      <c r="M3" s="197" t="s">
+      <c r="K3" s="181"/>
+      <c r="M3" s="182" t="s">
         <v>136</v>
       </c>
-      <c r="N3" s="198"/>
+      <c r="N3" s="183"/>
     </row>
     <row r="4" spans="2:26" s="1" customFormat="1">
       <c r="B4" s="7" t="s">
@@ -9320,22 +9329,22 @@
         <v>600000</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="191" t="s">
+      <c r="F3" s="176" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="193" t="s">
+      <c r="G3" s="177"/>
+      <c r="H3" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="194"/>
-      <c r="J3" s="195" t="s">
+      <c r="I3" s="179"/>
+      <c r="J3" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="K3" s="196"/>
-      <c r="M3" s="197" t="s">
+      <c r="K3" s="181"/>
+      <c r="M3" s="182" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="198"/>
+      <c r="N3" s="183"/>
     </row>
     <row r="4" spans="2:26" s="1" customFormat="1">
       <c r="B4" s="7" t="s">
